--- a/autoIt/ExportFiles/RDCubeExcelEntryNew.xlsx
+++ b/autoIt/ExportFiles/RDCubeExcelEntryNew.xlsx
@@ -20,7 +20,7 @@
     <t xml:space="preserve">RD Cube Department Tag</t>
   </si>
   <si>
-    <t xml:space="preserve">[As on date 18/05/2026]</t>
+    <t xml:space="preserve">[As on date 22/06/2026]</t>
   </si>
   <si>
     <t xml:space="preserve">Particulars</t>
